--- a/Result/profitability/8367.xlsx
+++ b/Result/profitability/8367.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.86625</v>
+        <v>0.7875000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>31.20125</v>
+        <v>30.495</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.77375</v>
+        <v>0.7075</v>
       </c>
       <c r="N3" t="n">
-        <v>30.5975</v>
+        <v>30.085</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.70875</v>
+        <v>0.62875</v>
       </c>
       <c r="N4" t="n">
-        <v>29.67875</v>
+        <v>29.13875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66625</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>28.80875</v>
+        <v>28.52875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6425000000000001</v>
+        <v>0.56625</v>
       </c>
       <c r="N6" t="n">
-        <v>28.0125</v>
+        <v>27.60875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6587500000000001</v>
+        <v>0.54125</v>
       </c>
       <c r="N7" t="n">
-        <v>27.51125</v>
+        <v>26.6375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -7540,6 +7540,133 @@
       </c>
       <c r="AM56" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>834</v>
+      </c>
+      <c r="D57" t="n">
+        <v>602</v>
+      </c>
+      <c r="E57" t="n">
+        <v>232</v>
+      </c>
+      <c r="F57" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>145</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>17.34%</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>-64</v>
+      </c>
+      <c r="J57" t="n">
+        <v>80</v>
+      </c>
+      <c r="K57" t="n">
+        <v>28</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N57" t="n">
+        <v>31.12875</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-0.5373134328358209</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-0.09999999999999787</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-0.003584229390680926</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-0.3700000000000001</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-0.5441176470588236</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-2.239999999999998</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>-0.07456724367509981</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
